--- a/outputs/Block6C_Variability_Metrics.xlsx
+++ b/outputs/Block6C_Variability_Metrics.xlsx
@@ -426,7 +426,7 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>50.615</v>
+        <v>51.751</v>
       </c>
       <c r="C2">
         <v>1.487</v>
@@ -440,7 +440,7 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>46.468</v>
+        <v>45.332</v>
       </c>
       <c r="C3">
         <v>1.243</v>
@@ -468,13 +468,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>224.524</v>
+        <v>233.456</v>
       </c>
       <c r="C5">
-        <v>10.956</v>
+        <v>13.142</v>
       </c>
       <c r="D5">
-        <v>0.049</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -482,13 +482,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>210.476</v>
+        <v>201.544</v>
       </c>
       <c r="C6">
-        <v>10.956</v>
+        <v>13.142</v>
       </c>
       <c r="D6">
-        <v>0.052</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -496,13 +496,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>48.941</v>
+        <v>50.077</v>
       </c>
       <c r="C7">
-        <v>2.02</v>
+        <v>1.863</v>
       </c>
       <c r="D7">
-        <v>0.041</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -510,13 +510,13 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>51.059</v>
+        <v>49.923</v>
       </c>
       <c r="C8">
-        <v>2.02</v>
+        <v>1.863</v>
       </c>
       <c r="D8">
-        <v>0.04</v>
+        <v>0.037</v>
       </c>
     </row>
   </sheetData>
